--- a/data/gravel/Boardman ADV 2025.xlsx
+++ b/data/gravel/Boardman ADV 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26773814-4CAC-0245-A701-894155683796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF52F7B-5CAC-BB48-B3B5-DA98395FAFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36220" yWindow="-19960" windowWidth="25020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4460" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -369,6 +369,9 @@
   </si>
   <si>
     <t>threaded</t>
+  </si>
+  <si>
+    <t>https://www.boardmanbikes.com/Assets/User/22168-Boardman_ADV_9.2_Alloy_Adventure_Gravel_Bike.jpg</t>
   </si>
 </sst>
 </file>
@@ -784,6 +787,9 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>

--- a/data/gravel/Boardman ADV 2025.xlsx
+++ b/data/gravel/Boardman ADV 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF52F7B-5CAC-BB48-B3B5-DA98395FAFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC21E95-D9D6-F64E-8405-68705D4A6BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4460" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -326,9 +326,6 @@
     <t>Boardman</t>
   </si>
   <si>
-    <t>pounds</t>
-  </si>
-  <si>
     <t>drop bar</t>
   </si>
   <si>
@@ -372,6 +369,15 @@
   </si>
   <si>
     <t>https://www.boardmanbikes.com/Assets/User/22168-Boardman_ADV_9.2_Alloy_Adventure_Gravel_Bike.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>Redditch, England, United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -739,7 +745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -759,7 +765,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -783,12 +789,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -822,7 +828,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>78</v>
@@ -1277,16 +1283,16 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C34" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="E34" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="F34" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>105</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>82</v>
@@ -1300,16 +1306,16 @@
         <v>30</v>
       </c>
       <c r="C35" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="E35" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="F35" s="7" t="s">
         <v>108</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>109</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>83</v>
@@ -1334,7 +1340,7 @@
         <v>68</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -1350,7 +1356,7 @@
         <v>31</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -1418,7 +1424,7 @@
         <v>42</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -1563,7 +1569,15 @@
         <v>65</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>97</v>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Boardman ADV 2025.xlsx
+++ b/data/gravel/Boardman ADV 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC21E95-D9D6-F64E-8405-68705D4A6BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2063615A-834A-1D45-82F8-23BC2E2E63C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -254,12 +254,6 @@
     <t>trail</t>
   </si>
   <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
-  </si>
-  <si>
     <t>Reach</t>
   </si>
   <si>
@@ -320,9 +314,6 @@
     <t>Handlebar Width</t>
   </si>
   <si>
-    <t>a8:f33</t>
-  </si>
-  <si>
     <t>Boardman</t>
   </si>
   <si>
@@ -378,6 +369,9 @@
   </si>
   <si>
     <t>Redditch, England, United Kingdom</t>
+  </si>
+  <si>
+    <t>a8:f31</t>
   </si>
 </sst>
 </file>
@@ -745,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -757,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -765,7 +759,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -789,12 +783,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -811,7 +805,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -828,19 +822,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="G8" s="6"/>
     </row>
@@ -849,7 +843,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" s="7">
         <v>559</v>
@@ -870,7 +864,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C10" s="7">
         <v>376</v>
@@ -891,7 +885,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C11" s="7">
         <v>515</v>
@@ -912,7 +906,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C12" s="7">
         <v>535</v>
@@ -933,7 +927,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C13" s="7">
         <v>130</v>
@@ -954,7 +948,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C14" s="7">
         <v>71</v>
@@ -975,7 +969,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C15" s="7">
         <v>74</v>
@@ -996,7 +990,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C16" s="7">
         <v>430</v>
@@ -1017,7 +1011,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C17" s="7">
         <v>50</v>
@@ -1038,7 +1032,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C18" s="7">
         <v>73</v>
@@ -1063,7 +1057,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C19" s="7">
         <v>170</v>
@@ -1084,7 +1078,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C20" s="7">
         <v>80</v>
@@ -1104,7 +1098,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C21" s="7">
         <v>400</v>
@@ -1210,20 +1204,16 @@
         <v>27</v>
       </c>
       <c r="C30" s="1">
-        <f>C32</f>
         <v>170</v>
       </c>
       <c r="D30" s="1">
-        <f>AVERAGE(D32,C33)</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E30" s="1">
-        <f t="shared" ref="E30:F30" si="0">AVERAGE(E32,D33)</f>
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F30" s="1">
-        <f t="shared" si="0"/>
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
@@ -1231,290 +1221,271 @@
         <v>28</v>
       </c>
       <c r="C31" s="1">
-        <f>D30</f>
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" ref="D31:E31" si="1">E30</f>
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E31" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F31" s="1">
-        <f>F33</f>
         <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="1">
-        <v>170</v>
-      </c>
-      <c r="D32" s="1">
-        <v>177</v>
-      </c>
-      <c r="E32" s="1">
-        <v>181</v>
-      </c>
-      <c r="F32" s="1">
-        <v>187</v>
+      <c r="C32" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" s="1">
-        <v>179</v>
-      </c>
-      <c r="D33" s="1">
-        <v>183</v>
-      </c>
-      <c r="E33" s="1">
-        <v>189</v>
-      </c>
-      <c r="F33" s="1">
-        <v>195</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C34" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>82</v>
-      </c>
+      <c r="A34" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="H35" s="4"/>
+        <v>94</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
+        <v>70</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="B40" s="1">
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B41" s="5"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B42" s="1">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B43" s="5"/>
+        <v>37</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="B46" s="1">
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="B47" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="1">
-        <v>142</v>
+        <v>42</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="1">
-        <v>100</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>110</v>
+        <v>44</v>
+      </c>
+      <c r="B50" s="1">
+        <v>31.6</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="1">
-        <v>31.6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="B61" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="B62" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63" s="1">
-        <v>2</v>
+        <v>57</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1</v>
+        <v>58</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>71</v>
@@ -1522,62 +1493,46 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="B69" s="1">
+        <v>850</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71" s="1">
-        <v>850</v>
+        <v>65</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Boardman ADV 2025.xlsx
+++ b/data/gravel/Boardman ADV 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2063615A-834A-1D45-82F8-23BC2E2E63C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CEE979-96BF-A54A-A1A1-BBAC014BAA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,24 @@
   </si>
   <si>
     <t>a8:f31</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -739,7 +757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1373,165 +1391,195 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="1">
-        <v>31.6</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B56" s="1">
+        <v>31.6</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B61" s="1">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B67" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="B68" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69" s="1">
-        <v>850</v>
+        <v>57</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="1">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>111</v>
       </c>
     </row>
